--- a/03_Outputs/Minero_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Minero_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E4" s="112">
-        <v>0.303462852400904</v>
+        <v>0.303462852400905</v>
       </c>
     </row>
     <row r="5">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="E6" s="112">
-        <v>0.370694540508038</v>
+        <v>0.370694540508037</v>
       </c>
     </row>
   </sheetData>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.303462852400904</v>
+        <v>0.303462852400905</v>
       </c>
     </row>
     <row r="3">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.370694540508038</v>
+        <v>0.370694540508037</v>
       </c>
     </row>
   </sheetData>
